--- a/companies/nl-ez/nl-ez-client-data-overview.xlsx
+++ b/companies/nl-ez/nl-ez-client-data-overview.xlsx
@@ -61,7 +61,7 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00666666"/>
+      <color rgb="00535353"/>
       <sz val="8"/>
     </font>
     <font>
@@ -82,7 +82,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -121,17 +121,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00535353"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0039870c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00e17000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00c63c2c"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00333333"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00535353"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -203,12 +213,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -724,7 +736,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -784,7 +796,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -814,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -891,7 +903,7 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>4.2 KB</t>
+          <t>5.6 KB</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -903,7 +915,7 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>fonts/RO-SansWebText-Bold.woff2</t>
+          <t>fonts/FiraSans-Bold.ttf</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
@@ -913,24 +925,24 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>WOFF2</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>47.6 KB</t>
+          <t>478.2 KB</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Font file — RO-SansWebText-Bold</t>
+          <t>Font file — FiraSans-Bold</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>fonts/RO-SansWebText-Italic.woff2</t>
+          <t>fonts/FiraSans-BoldItalic.ttf</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -940,24 +952,24 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>WOFF2</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>58.8 KB</t>
+          <t>495.0 KB</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>Font file — RO-SansWebText-Italic</t>
+          <t>Font file — FiraSans-BoldItalic</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>fonts/RO-SansWebText-Regular.woff2</t>
+          <t>fonts/FiraSans-Italic.ttf</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -967,24 +979,24 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>WOFF2</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>53.3 KB</t>
+          <t>461.3 KB</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Font file — RO-SansWebText-Regular</t>
+          <t>Font file — FiraSans-Italic</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>fonts/RO-SerifWeb-Italic.woff2</t>
+          <t>fonts/FiraSans-Medium.ttf</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -994,24 +1006,24 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>WOFF2</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>78.1 KB</t>
+          <t>446.5 KB</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>Font file — RO-SerifWeb-Italic</t>
+          <t>Font file — FiraSans-Medium</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>fonts/RO-SerifWeb-Regular.woff2</t>
+          <t>fonts/FiraSans-Regular.ttf</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
@@ -1021,353 +1033,353 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>WOFF2</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>65.6 KB</t>
+          <t>446.3 KB</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Font file — RO-SerifWeb-Regular</t>
+          <t>Font file — FiraSans-Regular</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>images/manifest.json</t>
+          <t>fonts/OFL-FiraSans.txt</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>2.5 KB</t>
+          <t>4.3 KB</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — OFL-FiraSans</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>images/photo-cover-01.jpg</t>
+          <t>fonts/OFL-SourceSerif4.txt</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>310.3 KB</t>
+          <t>4.3 KB</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — OFL-SourceSerif4</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>images/photo-cover-02.jpg</t>
+          <t>fonts/SourceSerif4-Italic[opsz,wght].ttf</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>100.0 KB</t>
+          <t>835.4 KB</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — SourceSerif4-Italic[opsz,wght]</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>images/photo-section-01.png</t>
+          <t>fonts/SourceSerif4[opsz,wght].ttf</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>105.3 KB</t>
+          <t>1181.2 KB</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — SourceSerif4[opsz,wght]</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>images/photo-section-02.jpg</t>
+          <t>fonts/web/RO-SansWebText-Bold.woff2</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>WOFF2</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>97.4 KB</t>
+          <t>47.6 KB</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — RO-SansWebText-Bold</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>images/photo-section-03.jpg</t>
+          <t>fonts/web/RO-SansWebText-Italic.woff2</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>WOFF2</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>54.0 KB</t>
+          <t>58.8 KB</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — RO-SansWebText-Italic</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>images/photo-section-04.jpg</t>
+          <t>fonts/web/RO-SansWebText-Regular.woff2</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>WOFF2</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>40.5 KB</t>
+          <t>53.3 KB</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — RO-SansWebText-Regular</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>logos/apple-touch-icon.png</t>
+          <t>fonts/web/RO-SerifWeb-Italic.woff2</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>WOFF2</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>5.7 KB</t>
+          <t>78.1 KB</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Logo asset — apple-touch-icon</t>
+          <t>Font file — RO-SerifWeb-Italic</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>logos/favicon.ico</t>
+          <t>fonts/web/RO-SerifWeb-Regular.woff2</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>ICO</t>
+          <t>WOFF2</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>1.1 KB</t>
+          <t>65.6 KB</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>Logo asset — favicon</t>
+          <t>Font file — RO-SerifWeb-Regular</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>logos/logo-mark-alt.svg</t>
+          <t>images/manifest.json</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>18.4 KB</t>
+          <t>2.5 KB</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Logo asset — logo-mark-alt</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>logos/logo-wordmark.png</t>
+          <t>images/photo-cover-01.jpg</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>9.1 KB</t>
+          <t>310.3 KB</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>Logo asset — logo-wordmark</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>logos/logo-wordmark.svg</t>
+          <t>images/photo-cover-02.jpg</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>31.4 KB</t>
+          <t>100.0 KB</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Logo asset — logo-wordmark</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>logos/logo.png</t>
+          <t>images/photo-section-01.png</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -1377,105 +1389,105 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>4.5 KB</t>
+          <t>105.3 KB</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>Logo asset — logo</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>logos/logo.svg</t>
+          <t>images/photo-section-02.jpg</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>16.8 KB</t>
+          <t>97.4 KB</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Logo asset — logo</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>pptx-assets/gradient-accent.png</t>
+          <t>images/photo-section-03.jpg</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>8.6 KB</t>
+          <t>54.0 KB</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>Gradient / motif asset for PowerPoint backgrounds</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>pptx-assets/gradient-dark.png</t>
+          <t>images/photo-section-04.jpg</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>8.8 KB</t>
+          <t>40.5 KB</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Gradient / motif asset for PowerPoint backgrounds</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>pptx-assets/gradient-light.png</t>
+          <t>logos/apple-touch-icon.png</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -1485,207 +1497,477 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>9.0 KB</t>
+          <t>5.7 KB</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>Gradient / motif asset for PowerPoint backgrounds</t>
+          <t>Logo asset — apple-touch-icon</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/photo-cover-01-overlay.jpg</t>
+          <t>logos/favicon.ico</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>ICO</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>240.3 KB</t>
+          <t>1.1 KB</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Logo asset — favicon</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/photo-cover-02-overlay.jpg</t>
+          <t>logos/logo-mark-alt.svg</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>SVG</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>103.6 KB</t>
+          <t>18.4 KB</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Logo asset — logo-mark-alt</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/photo-section-01-overlay.jpg</t>
+          <t>logos/logo-wordmark.png</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>21.3 KB</t>
+          <t>9.1 KB</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Logo asset — logo-wordmark</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/photo-section-02-overlay.jpg</t>
+          <t>logos/logo-wordmark.svg</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>SVG</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>55.3 KB</t>
+          <t>31.4 KB</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Logo asset — logo-wordmark</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/photo-section-03-overlay.jpg</t>
+          <t>logos/logo.png</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>55.3 KB</t>
+          <t>4.5 KB</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Logo asset — logo</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>pptx-assets/overlays/photo-section-04-overlay.jpg</t>
+          <t>logos/logo.svg</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>pptx-assets</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>SVG</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>19.8 KB</t>
+          <t>16.8 KB</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>Pre-composited overlay image for PowerPoint</t>
+          <t>Logo asset — logo</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
+          <t>nl-ez-client-data-overview.xlsx</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>XLSX</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>11.8 KB</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>pptx-assets/gradient-accent.png</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>pptx-assets</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>PNG</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>8.6 KB</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>Gradient / motif asset for PowerPoint backgrounds</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>pptx-assets/gradient-dark.png</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>pptx-assets</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>PNG</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>8.8 KB</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>Gradient / motif asset for PowerPoint backgrounds</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>pptx-assets/gradient-light.png</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>pptx-assets</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>PNG</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>9.0 KB</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>Gradient / motif asset for PowerPoint backgrounds</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>pptx-assets/overlays/photo-cover-01-overlay.jpg</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>pptx-assets</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>JPEG</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>240.3 KB</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>Pre-composited overlay image for PowerPoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>pptx-assets/overlays/photo-cover-02-overlay.jpg</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>pptx-assets</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>JPEG</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>103.6 KB</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>Pre-composited overlay image for PowerPoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>pptx-assets/overlays/photo-section-01-overlay.jpg</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>pptx-assets</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>JPEG</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>21.3 KB</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>Pre-composited overlay image for PowerPoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>pptx-assets/overlays/photo-section-02-overlay.jpg</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>pptx-assets</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>JPEG</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>55.3 KB</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Pre-composited overlay image for PowerPoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>pptx-assets/overlays/photo-section-03-overlay.jpg</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>pptx-assets</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>JPEG</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>55.3 KB</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>Pre-composited overlay image for PowerPoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>pptx-assets/overlays/photo-section-04-overlay.jpg</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>pptx-assets</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>JPEG</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>19.8 KB</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>Pre-composited overlay image for PowerPoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
           <t>tokens.css</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>root</t>
         </is>
       </c>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>CSS</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D44" s="11" t="inlineStr">
         <is>
           <t>1.1 KB</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>CSS design tokens mapping brand colors to CSS variables</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="8" customHeight="1"/>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+    <row r="45" ht="8" customHeight="1"/>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>Ministerie van Economische Zaken en Klimaat  ·  Confidential — Not for distribution</t>
         </is>
@@ -1693,8 +1975,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A46:F46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1706,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1881,22 +2163,22 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Background</t>
+          <t>Textlight</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>#FFFFFF</t>
+          <t>#535353</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>rgb(255, 255, 255)</t>
+          <t>rgb(83, 83, 83)</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>Page / sheet background</t>
+          <t>Captions, footers, secondary labels</t>
         </is>
       </c>
     </row>
@@ -1908,22 +2190,22 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Surface</t>
+          <t>Background</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>#F3F3F3</t>
+          <t>#FFFFFF</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>rgb(243, 243, 243)</t>
+          <t>rgb(255, 255, 255)</t>
         </is>
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>Alternating rows, card backgrounds</t>
+          <t>Page / sheet background</t>
         </is>
       </c>
     </row>
@@ -1935,22 +2217,22 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Surface</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>#C63C2C</t>
+          <t>#F3F3F3</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>rgb(198, 60, 44)</t>
+          <t>rgb(243, 243, 243)</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>Error / danger state</t>
+          <t>Alternating rows, card backgrounds</t>
         </is>
       </c>
     </row>
@@ -1962,22 +2244,22 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>Text Body</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>#333333</t>
+          <t>#39870C</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>rgb(51, 51, 51)</t>
+          <t>rgb(57, 135, 12)</t>
         </is>
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t>Additional brand color</t>
+          <t>Success / positive state</t>
         </is>
       </c>
     </row>
@@ -1989,22 +2271,22 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Text Meta</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>#535353</t>
+          <t>#E17000</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>rgb(83, 83, 83)</t>
+          <t>rgb(225, 112, 0)</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>Additional brand color</t>
+          <t>Warning / caution state</t>
         </is>
       </c>
     </row>
@@ -2016,55 +2298,163 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>#C63C2C</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>rgb(198, 60, 44)</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>Error / danger state</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Text Body</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>#333333</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>rgb(51, 51, 51)</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>Additional brand color</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Text Meta</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>#535353</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>rgb(83, 83, 83)</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>Additional brand color</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Backgroundalt</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>#F3F3F3</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>rgb(243, 243, 243)</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>Additional brand color</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   </t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
           <t>Border</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>#E6E6E6</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>rgb(230, 230, 230)</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>Additional brand color</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">   </t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>#FFFFFF</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>rgb(255, 255, 255)</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>Additional brand color</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="8" customHeight="1"/>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="20" ht="8" customHeight="1"/>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Ministerie van Economische Zaken en Klimaat  ·  Confidential — Not for distribution</t>
         </is>
@@ -2072,8 +2462,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A21:F21"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2152,7 +2542,7 @@
       <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Heading</t>
         </is>
@@ -2184,7 +2574,7 @@
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Body</t>
         </is>
@@ -2216,7 +2606,7 @@
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Serif</t>
         </is>
@@ -2283,7 +2673,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>fonts/RO-SansWebText-Regular.woff2</t>
+          <t>fonts/web/RO-SansWebText-Regular.woff2</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2685,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>fonts/RO-SansWebText-Bold.woff2</t>
+          <t>fonts/web/RO-SansWebText-Bold.woff2</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2697,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>fonts/RO-SansWebText-Italic.woff2</t>
+          <t>fonts/web/RO-SansWebText-Italic.woff2</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2709,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>fonts/RO-SerifWeb-Regular.woff2</t>
+          <t>fonts/web/RO-SerifWeb-Regular.woff2</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2721,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>fonts/RO-SerifWeb-Italic.woff2</t>
+          <t>fonts/web/RO-SerifWeb-Italic.woff2</t>
         </is>
       </c>
     </row>
